--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>358666.7561825999</v>
+        <v>358667</v>
       </c>
       <c r="R3" t="n">
-        <v>6400556.646552895</v>
+        <v>6400557</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1995-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>358666.7561825999</v>
+        <v>358667</v>
       </c>
       <c r="R2" t="n">
-        <v>6400556.646552895</v>
+        <v>6400557</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-08-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98475</v>
+        <v>98483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98523</v>
+        <v>98536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 65506-2020 artfynd.xlsx
+++ b/artfynd/A 65506-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2445786</v>
       </c>
       <c r="B2" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4211979</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
